--- a/Lasser_Driver_v5/pm6V/pm6V_BOM_digikey_priced.xlsx
+++ b/Lasser_Driver_v5/pm6V/pm6V_BOM_digikey_priced.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R37"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="8" max="8"/>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>6849</v>
+        <v>6549</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
         <v>1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="O2" s="2">
         <f>N2*L2</f>
@@ -672,7 +672,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="O3" s="2">
         <f>N3*L3</f>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>66025</v>
+        <v>62711</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>76328</v>
+        <v>43157</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>5506</v>
+        <v>5467</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="O6" s="2">
         <f>N6*L6</f>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>17395</v>
+        <v>2704659</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>85781</v>
+        <v>85646</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>19731</v>
+        <v>19147</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>24960</v>
+        <v>24232</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>68517</v>
+        <v>67659</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>2057</v>
+        <v>2007</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>15105</v>
+        <v>13890</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IRF540NPBF</t>
+          <t>IRF540ZPBF</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IRF540N</t>
+          <t>IRF540Z</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>N-MOSFET 100V 33A TO-220 (pos pre-reg pass)</t>
+          <t>N-MOSFET 100V 36A TO-220 (pos pre-reg pass; IRF540N replacement)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>IRF540NPBF-ND</t>
+          <t>IRF540ZPBF-ND</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>5</v>
+        <v>49233</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>1.93</v>
+        <v>2.34</v>
       </c>
       <c r="O19" s="2">
         <f>N19*L19</f>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>https://www.infineon.com/assets/row/public/documents/24/49/infineon-irf540n-datasheet-en.pdf</t>
+          <t>https://www.infineon.com/dgdl/irf540zpbf.pdf?fileId=5546d462533600a4015355e3af7d19a6</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>12122</v>
+        <v>11781</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="O20" s="2">
         <f>N20*L20</f>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>101784</v>
+        <v>245269</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>70875</v>
+        <v>31839</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>322</v>
+        <v>207</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>605964</v>
+        <v>557538</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>251502</v>
+        <v>227630</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>307847</v>
+        <v>227069</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>328505</v>
+        <v>309898</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>134082</v>
+        <v>129064</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>941216</v>
+        <v>880408</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>88155</v>
+        <v>59927</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>1887</v>
+        <v>1525</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2926,24 +2926,304 @@
       <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="N35" s="2" t="n"/>
-      <c r="O35" s="2" t="n"/>
+      <c r="A35" t="n">
+        <v>4</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PMSSS 440 0050 PH</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>B&amp;F Fastener Supply</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>pm6V Q7-Q10 (TO-264 mount)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>#4-40 x 1/2in screw</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Hardware (off-PCB)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>SS pan-head machine screw #4-40 x 1/2in; TO-264 tab-&gt;657 heatsink (verify length vs boss, 3/8in alt)</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>H705-ND</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>BFirst Industrial</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>18671</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>4</v>
+      </c>
+      <c r="M35" t="n">
+        <v>100</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="O35" s="2">
+        <f>N35*L35</f>
+        <v/>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>http://www.fasnetdirect.com/refguide/Machinescrewthreads.pdf</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="N36" s="3" t="inlineStr">
+      <c r="A36" t="n">
+        <v>4</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>FWSS 004</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>B&amp;F Fastener Supply</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>pm6V Q7-Q10 (TO-264 mount)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>#4 flat washer</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Hardware (off-PCB)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SS #4 flat washer, nut side</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>H734-ND</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>BFirst Industrial</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>24341</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>4</v>
+      </c>
+      <c r="M36" t="n">
+        <v>100</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>0.0183</v>
+      </c>
+      <c r="O36" s="2">
+        <f>N36*L36</f>
+        <v/>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>4</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>INTLWZ 004</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>B&amp;F Fastener Supply</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>pm6V Q7-Q10 (TO-264 mount)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>#4 int-tooth lock washer</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Hardware (off-PCB)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Internal-tooth lock washer #4 (anti-loosen under nut, thermal cycling)</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>H236-ND</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>BFirst Industrial</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>15796</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>4</v>
+      </c>
+      <c r="M37" t="n">
+        <v>100</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="O37" s="2">
+        <f>N37*L37</f>
+        <v/>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>//mm.digikey.com/Volume0/opasdata/d220001/medias/docus/8325/INTLWZ-004-Datasheet.pdf</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>4</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>HNZ 440</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>B&amp;F Fastener Supply</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>pm6V Q7-Q10 (TO-264 mount)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>#4-40 hex nut</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Hardware (off-PCB)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>#4-40 hex nut, zinc-plated steel</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>H216-ND</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>BFirst Industrial</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>26939</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>4</v>
+      </c>
+      <c r="M38" t="n">
+        <v>100</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="O38" s="2">
+        <f>N38*L38</f>
+        <v/>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="N40" s="3" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="O36" s="3">
-        <f>SUM(O2:O34)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>Prices pulled 2026-07-02 06:38 (USD), 1 board(s)</t>
+      <c r="O40" s="3">
+        <f>SUM(O2:O38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Prices pulled 2026-07-13 10:41 (USD), 1 board(s)</t>
         </is>
       </c>
     </row>

--- a/Lasser_Driver_v5/pm6V/pm6V_BOM_digikey_priced.xlsx
+++ b/Lasser_Driver_v5/pm6V/pm6V_BOM_digikey_priced.xlsx
@@ -611,7 +611,6 @@
           <t>https://www.nichicon.co.jp/english/series_items/catalog_pdf/e-uhe.pdf</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -683,7 +682,6 @@
           <t>https://www.nichicon.co.jp/english/series_items/catalog_pdf/e-uhe.pdf</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -755,7 +753,6 @@
           <t>http://www.samsungsem.com/kr/support/product-search/mlcc/CL21B474KBFNNNE.jsp</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -827,7 +824,6 @@
           <t>https://weblib.samsungsem.com/mlcc/mlcc-ec-data-sheet.do?partNumber=CL21B225KBYNNW</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -899,7 +895,6 @@
           <t>https://www.nichicon.co.jp/english/series_items/catalog_pdf/e-uvz.pdf</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -971,7 +966,6 @@
           <t>https://www.diodes.com/assets/Datasheets/BAV16W_1N4148W.pdf</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1119,7 +1113,6 @@
           <t>https://www.onsemi.com/pdf/datasheet/1n4736at-d.pdf</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1191,7 +1184,6 @@
           <t>https://info.boydcorp.com/hubfs/Thermal/Air-Cooling/Boyd-Board-Level-Heatsinks-Catalog.pdf</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1263,7 +1255,6 @@
           <t>https://info.boydcorp.com/hubfs/Thermal/Air-Cooling/Boyd-Board-Level-Heatsinks-Catalog.pdf</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1335,7 +1326,6 @@
           <t>//mm.digikey.com/Volume0/opasdata/d220001/medias/docus/1883/Wakefield-657-15ABPE-datasheet.pdf</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1407,7 +1397,6 @@
           <t>https://info.boydcorp.com/hubfs/Thermal/Air-Cooling/Boyd-Board-Level-Heatsinks-Catalog.pdf</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1479,7 +1468,6 @@
           <t>//mm.digikey.com/Volume0/opasdata/d220001/medias/docus/7343/Wakefield_Thermal%20Insulators%20Catalog_9-15-2025.pdf</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1551,7 +1539,6 @@
           <t>https://info.boydcorp.com/hubfs/Thermal/Air-Cooling/Boyd-Board-Level-Heatsinks-Catalog.pdf</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1623,7 +1610,6 @@
           <t>https://www.tglobaltechnology.com/wp-content/uploads/2023/08/TG-A3500_UK.pdf</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1695,7 +1681,6 @@
           <t>//mm.digikey.com/Volume0/opasdata/d220001/medias/docus/5784/MKDSN%201%2C5_%203-5%2C08.pdf</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1843,7 +1828,6 @@
           <t>https://www.infineon.com/dgdl/irf540zpbf.pdf?fileId=5546d462533600a4015355e3af7d19a6</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1915,7 +1899,6 @@
           <t>https://www.infineon.com/assets/row/public/documents/24/49/infineon-irf9540n-datasheet-en.pdf</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1987,7 +1970,6 @@
           <t>https://www.mccsemi.com/pdf/Products/MMBT2907A(SOT-23).pdf</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2059,7 +2041,6 @@
           <t>https://www.onsemi.com/pdf/datasheet/mmbt2222lt1-d.pdf</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2131,7 +2112,6 @@
           <t>https://www.onsemi.com/pdf/datasheet/mjl21193-d.pdf</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2203,7 +2183,6 @@
           <t>https://www.onsemi.com/pdf/datasheet/mjl21193-d.pdf</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2275,7 +2254,6 @@
           <t>https://www.ohmite.com/assets/images/res-tuw-tum.pdf</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2347,7 +2325,6 @@
           <t>https://yageogroup.com/content/datasheet/asset/file/PYU-RC_GROUP_51_ROHS_L</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2365,7 +2342,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>pm6V R24,R31</t>
+          <t>pm6V R25,R30</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2419,7 +2396,6 @@
           <t>https://yageogroup.com/content/datasheet/asset/file/PYU-RC_GROUP_51_ROHS_L</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2437,7 +2413,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>pm6V R25,R30</t>
+          <t>pm6V R24,R31</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2491,7 +2467,6 @@
           <t>https://industrial.panasonic.com/cdbs/www-data/pdf/RDA0000/AOA0000C304.pdf</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2563,7 +2538,6 @@
           <t>https://yageogroup.com/content/datasheet/asset/file/PYU-RC_GROUP_51_ROHS_L</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2635,7 +2609,6 @@
           <t>https://yageogroup.com/content/datasheet/asset/file/PYU-RC_GROUP_51_ROHS_L</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2707,7 +2680,6 @@
           <t>https://www.vishay.com/docs/30100/wsl.pdf</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2779,7 +2751,6 @@
           <t>https://www.vishay.com/docs/20035/dcrcwe3.pdf</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2851,7 +2822,6 @@
           <t>https://yageogroup.com/content/datasheet/asset/file/PYU-RC_GROUP_51_ROHS_L</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2923,7 +2893,6 @@
           <t>https://rocelec.widen.net/view/pdf/laxdfeqisn/lm4051-n.pdf?t.download=true&amp;u=5oefqw</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2995,7 +2964,6 @@
           <t>http://www.fasnetdirect.com/refguide/Machinescrewthreads.pdf</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3062,8 +3030,6 @@
         <f>N36*L36</f>
         <v/>
       </c>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3135,7 +3101,6 @@
           <t>//mm.digikey.com/Volume0/opasdata/d220001/medias/docus/8325/INTLWZ-004-Datasheet.pdf</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3202,8 +3167,6 @@
         <f>N38*L38</f>
         <v/>
       </c>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="N39" s="2" t="n"/>

--- a/Lasser_Driver_v5/pm6V/pm6V_BOM_digikey_priced.xlsx
+++ b/Lasser_Driver_v5/pm6V/pm6V_BOM_digikey_priced.xlsx
@@ -1277,7 +1277,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Heatsink TO-264 vert 1in</t>
+          <t>Heatsink TO-264 [REPLACE-DOES NOT FIT]</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Vert board-mount heatsink 657-series 1in ~10C/W for TO-264 pass Q7-Q10; fits 100x160 Eurocard</t>
+          <t>*** DOES NOT FIT TO-264 (channel ~16mm &lt; 20mm device) *** REPLACE with clip-on OMNI-UNI-PF-38 + OMNI-UC clip (Wakefield-Vette, DK 345-1600-ND / 345-1493-ND); clip mount leaves the 25.4mm pin holes unused. Trialing before permanent change.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1324,6 +1324,11 @@
       <c r="Q12" t="inlineStr">
         <is>
           <t>//mm.digikey.com/Volume0/opasdata/d220001/medias/docus/1883/Wakefield-657-15ABPE-datasheet.pdf</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>DOES NOT FIT TO-264 - replace w/ OMNI-UNI-PF-38 + OMNI-UC (trial)</t>
         </is>
       </c>
     </row>
